--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -461,10 +461,10 @@
         <v>30</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="E4" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
     </row>
   </sheetData>
